--- a/backend/wp_templates/N/N3 递延所得税负债.xlsx
+++ b/backend/wp_templates/N/N3 递延所得税负债.xlsx
@@ -4291,7 +4291,7 @@
       </c>
       <c r="H10" s="29" t="inlineStr">
         <is>
-          <t>递延所得税资产期初审定数</t>
+          <t>递延所得税负债期初审定数</t>
         </is>
       </c>
       <c r="I10" s="29" t="inlineStr">
@@ -4345,7 +4345,7 @@
       <c r="F11" s="202" t="n"/>
       <c r="G11" s="202" t="n"/>
       <c r="H11" s="204">
-        <f>F11+O3</f>
+        <f>E11+F11+G11</f>
         <v/>
       </c>
       <c r="I11" s="202" t="n"/>
@@ -4357,7 +4357,7 @@
       <c r="L11" s="202" t="n"/>
       <c r="M11" s="202" t="n"/>
       <c r="N11" s="205">
-        <f>L11+K11</f>
+        <f>K11+L11+M11</f>
         <v/>
       </c>
     </row>
@@ -4381,7 +4381,7 @@
       <c r="F12" s="202" t="n"/>
       <c r="G12" s="202" t="n"/>
       <c r="H12" s="204">
-        <f>F12+O4</f>
+        <f>E12+F12+G12</f>
         <v/>
       </c>
       <c r="I12" s="202" t="n"/>
@@ -4393,7 +4393,7 @@
       <c r="L12" s="202" t="n"/>
       <c r="M12" s="202" t="n"/>
       <c r="N12" s="205">
-        <f>L12+K12</f>
+        <f>K12+L12+M12</f>
         <v/>
       </c>
     </row>
@@ -4417,7 +4417,7 @@
       <c r="F13" s="202" t="n"/>
       <c r="G13" s="202" t="n"/>
       <c r="H13" s="204">
-        <f>F13+O5</f>
+        <f>E13+F13+G13</f>
         <v/>
       </c>
       <c r="I13" s="202" t="n"/>
@@ -4429,7 +4429,7 @@
       <c r="L13" s="202" t="n"/>
       <c r="M13" s="202" t="n"/>
       <c r="N13" s="205">
-        <f>L13+K13</f>
+        <f>K13+L13+M13</f>
         <v/>
       </c>
     </row>
@@ -4453,7 +4453,7 @@
       <c r="F14" s="202" t="n"/>
       <c r="G14" s="202" t="n"/>
       <c r="H14" s="204">
-        <f>F14+O6</f>
+        <f>E14+F14+G14</f>
         <v/>
       </c>
       <c r="I14" s="202" t="n"/>
@@ -4465,7 +4465,7 @@
       <c r="L14" s="202" t="n"/>
       <c r="M14" s="202" t="n"/>
       <c r="N14" s="205">
-        <f>L14+K14</f>
+        <f>K14+L14+M14</f>
         <v/>
       </c>
     </row>
@@ -4489,7 +4489,7 @@
       <c r="F15" s="202" t="n"/>
       <c r="G15" s="202" t="n"/>
       <c r="H15" s="204">
-        <f>F15+O7</f>
+        <f>E15+F15+G15</f>
         <v/>
       </c>
       <c r="I15" s="202" t="n"/>
@@ -4501,7 +4501,7 @@
       <c r="L15" s="202" t="n"/>
       <c r="M15" s="202" t="n"/>
       <c r="N15" s="205">
-        <f>L15+K15</f>
+        <f>K15+L15+M15</f>
         <v/>
       </c>
     </row>
@@ -4525,7 +4525,7 @@
       <c r="F16" s="202" t="n"/>
       <c r="G16" s="202" t="n"/>
       <c r="H16" s="204">
-        <f>F16+O8</f>
+        <f>E16+F16+G16</f>
         <v/>
       </c>
       <c r="I16" s="202" t="n"/>
@@ -4537,7 +4537,7 @@
       <c r="L16" s="202" t="n"/>
       <c r="M16" s="202" t="n"/>
       <c r="N16" s="205">
-        <f>L16+K16</f>
+        <f>K16+L16+M16</f>
         <v/>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       <c r="F17" s="202" t="n"/>
       <c r="G17" s="202" t="n"/>
       <c r="H17" s="204">
-        <f>F17+O9</f>
+        <f>E17+F17+G17</f>
         <v/>
       </c>
       <c r="I17" s="202" t="n"/>
@@ -4573,7 +4573,7 @@
       <c r="L17" s="202" t="n"/>
       <c r="M17" s="202" t="n"/>
       <c r="N17" s="205">
-        <f>L17+K17</f>
+        <f>K17+L17+M17</f>
         <v/>
       </c>
     </row>
@@ -4597,7 +4597,7 @@
       <c r="F18" s="202" t="n"/>
       <c r="G18" s="202" t="n"/>
       <c r="H18" s="204">
-        <f>F18+O10</f>
+        <f>E18+F18+G18</f>
         <v/>
       </c>
       <c r="I18" s="202" t="n"/>
@@ -4609,7 +4609,7 @@
       <c r="L18" s="202" t="n"/>
       <c r="M18" s="202" t="n"/>
       <c r="N18" s="205">
-        <f>L18+K18</f>
+        <f>K18+L18+M18</f>
         <v/>
       </c>
     </row>
@@ -4633,7 +4633,7 @@
       <c r="F19" s="202" t="n"/>
       <c r="G19" s="202" t="n"/>
       <c r="H19" s="204">
-        <f>F19+O11</f>
+        <f>E19+F19+G19</f>
         <v/>
       </c>
       <c r="I19" s="202" t="n"/>
@@ -4645,7 +4645,7 @@
       <c r="L19" s="202" t="n"/>
       <c r="M19" s="202" t="n"/>
       <c r="N19" s="205">
-        <f>L19+K19</f>
+        <f>K19+L19+M19</f>
         <v/>
       </c>
     </row>
@@ -4669,7 +4669,7 @@
       <c r="F20" s="202" t="n"/>
       <c r="G20" s="202" t="n"/>
       <c r="H20" s="204">
-        <f>F20+O12</f>
+        <f>E20+F20+G20</f>
         <v/>
       </c>
       <c r="I20" s="202" t="n"/>
@@ -4681,7 +4681,7 @@
       <c r="L20" s="202" t="n"/>
       <c r="M20" s="202" t="n"/>
       <c r="N20" s="205">
-        <f>L20+K20</f>
+        <f>K20+L20+M20</f>
         <v/>
       </c>
     </row>
@@ -4701,7 +4701,7 @@
       <c r="F21" s="202" t="n"/>
       <c r="G21" s="202" t="n"/>
       <c r="H21" s="204">
-        <f>F21+O13</f>
+        <f>E21+F21+G21</f>
         <v/>
       </c>
       <c r="I21" s="202" t="n"/>
@@ -4713,7 +4713,7 @@
       <c r="L21" s="202" t="n"/>
       <c r="M21" s="202" t="n"/>
       <c r="N21" s="205">
-        <f>L21+K21</f>
+        <f>K21+L21+M21</f>
         <v/>
       </c>
     </row>
@@ -4742,14 +4742,16 @@
       </c>
       <c r="D23" s="204" t="n"/>
       <c r="E23" s="204">
-        <f>SUM(E3:O22)</f>
+        <f>SUM(E11:E22)</f>
         <v/>
       </c>
       <c r="F23" s="204">
         <f>SUM(F11:F22)</f>
         <v/>
       </c>
-      <c r="G23" s="204" t="n"/>
+      <c r="G23" s="204">
+        <f>SUM(G11:G22)</f>
+      </c>
       <c r="H23" s="204">
         <f>SUM(H11:H22)</f>
         <v/>
@@ -4767,7 +4769,9 @@
         <f>SUM(L11:L22)</f>
         <v/>
       </c>
-      <c r="M23" s="204" t="n"/>
+      <c r="M23" s="204">
+        <f>SUM(M11:M22)</f>
+      </c>
       <c r="N23" s="204">
         <f>SUM(N11:N22)</f>
         <v/>
